--- a/mesh_shadowgraphs.xlsx
+++ b/mesh_shadowgraphs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desde\Downloads\main (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95615C05-B623-42DE-A8B5-1441028571B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286E0DF-E64E-4280-BDDD-65518CA462CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E167558C-EDAE-441A-9DD3-8D69DFB345C7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
   <si>
     <t>Option 1: Parralel beam</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>200 mesh</t>
+  </si>
+  <si>
+    <t>300 mesh</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290997F1-A6F2-4FC0-8773-DC0DE9C8F7BD}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.6640625" customWidth="1"/>
@@ -599,10 +602,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
         <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -632,10 +635,10 @@
         <v>3</v>
       </c>
       <c r="B22">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="C22">
         <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="C22">
-        <v>5.0999999999999997E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -666,10 +669,10 @@
         <v>10</v>
       </c>
       <c r="B26" s="2">
-        <v>55.128</v>
+        <v>38</v>
       </c>
       <c r="C26" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -678,11 +681,11 @@
       </c>
       <c r="B27" s="1">
         <f>B26*B24</f>
-        <v>3.0320399999999998</v>
+        <v>2.09</v>
       </c>
       <c r="C27" s="1">
         <f>C26*C24</f>
-        <v>2.75</v>
+        <v>3.0249999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -691,11 +694,11 @@
       </c>
       <c r="B28" s="1">
         <f>B26*(B22+B23)/B22</f>
-        <v>74.939624999999992</v>
+        <v>55.137254901960787</v>
       </c>
       <c r="C28" s="1">
         <f>C26*(C22+C23)/C22</f>
-        <v>72.549019607843135</v>
+        <v>74.765624999999986</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -704,11 +707,11 @@
       </c>
       <c r="B29">
         <f>B28*B24</f>
-        <v>4.1216793749999994</v>
+        <v>3.0325490196078433</v>
       </c>
       <c r="C29">
         <f>C28*C24</f>
-        <v>3.9901960784313726</v>
+        <v>4.1121093749999993</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -717,11 +720,11 @@
       </c>
       <c r="B31">
         <f>B21/(B29/B22-1)</f>
-        <v>1.7349818330582121</v>
+        <v>1.8815722844422229</v>
       </c>
       <c r="C31">
         <f>C21/(C29/C22-1)</f>
-        <v>1.4241484527050907</v>
+        <v>1.7390834455899555</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -730,11 +733,11 @@
       </c>
       <c r="B32">
         <f>B20-B31</f>
-        <v>8.2650181669417879</v>
+        <v>8.1184277155577771</v>
       </c>
       <c r="C32">
         <f>C20-C31</f>
-        <v>8.5758515472949099</v>
+        <v>8.2609165544100449</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -755,7 +758,7 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -763,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="B38">
-        <v>0.127</v>
+        <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -771,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="B39">
-        <v>2.5999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -796,7 +799,7 @@
         <v>10</v>
       </c>
       <c r="B43" s="2">
-        <v>40.216999999999999</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +808,7 @@
       </c>
       <c r="B44" s="1">
         <f>B43*B40</f>
-        <v>2.211935</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -814,7 +817,7 @@
       </c>
       <c r="B45" s="1">
         <f>B43*(B38+B39)/B38</f>
-        <v>48.450401574803145</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="C45" s="1"/>
     </row>
@@ -824,7 +827,7 @@
       </c>
       <c r="B46">
         <f>B45*B40</f>
-        <v>2.6647720866141729</v>
+        <v>2.2776470588235296</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -833,146 +836,194 @@
       </c>
       <c r="B48">
         <f>B37/(B46/B38-1)</f>
-        <v>4.503950555800146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5.427230046948357</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
       <c r="B49">
         <f>B36-B48</f>
-        <v>15.496049444199855</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>14.572769953051644</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>19</v>
       </c>
       <c r="B50">
         <f>B49*B41/(B49+B41)</f>
-        <v>8.7311403307344388</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+        <v>8.4302009777294948</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>1</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>20</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="C55">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>2</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>90</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="C56">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>3</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>0.127</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="C57">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>2.5999999999999999E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="C58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>4</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>5.5E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="C59">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>16</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>20</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="C60">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="2">
-        <v>34.82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="B62" s="2">
+        <v>35</v>
+      </c>
+      <c r="C62" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="1">
-        <f>B61*B58</f>
-        <v>1.9151</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="B63" s="1">
+        <f>B62*B59</f>
+        <v>1.925</v>
+      </c>
+      <c r="C63" s="1">
+        <f>C62*C59</f>
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>5</v>
       </c>
-      <c r="B63" s="1">
-        <f>B61*(B56+B57)/B56</f>
-        <v>41.948503937007878</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B64" s="1">
+        <f>B62*(B57+B58)/B57</f>
+        <v>42.165354330708659</v>
+      </c>
+      <c r="C64" s="1">
+        <f>C62*(C57+C58)/C57</f>
+        <v>41.411764705882355</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>6</v>
       </c>
-      <c r="B64">
-        <f>B63*B58</f>
-        <v>2.3071677165354334</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="B65">
+        <f>B64*B59</f>
+        <v>2.3190944881889761</v>
+      </c>
+      <c r="C65">
+        <f>C64*C59</f>
+        <v>2.2776470588235296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>17</v>
       </c>
-      <c r="B66">
-        <f>B55/(B64/B56-1)</f>
-        <v>5.2427159219492241</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="B67">
+        <f>B56/(B65/B57-1)</f>
+        <v>5.2141912958519532</v>
+      </c>
+      <c r="C67">
+        <f>C56/(C65/C57-1)</f>
+        <v>5.427230046948357</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>18</v>
       </c>
-      <c r="B67">
-        <f>B54-B66</f>
-        <v>14.757284078050777</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="B68">
+        <f>B55-B67</f>
+        <v>14.785808704148046</v>
+      </c>
+      <c r="C68">
+        <f>C55-C67</f>
+        <v>14.572769953051644</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>19</v>
       </c>
-      <c r="B68">
-        <f>B67*B59/(B67+B59)</f>
-        <v>8.4916209476620192</v>
+      <c r="B69">
+        <f>B68*B60/(B68+B60)</f>
+        <v>8.5010579054813853</v>
+      </c>
+      <c r="C69">
+        <f>C68*C60/(C68+C60)</f>
+        <v>8.4302009777294948</v>
       </c>
     </row>
   </sheetData>

--- a/mesh_shadowgraphs.xlsx
+++ b/mesh_shadowgraphs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desde\Downloads\main (1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desde\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286E0DF-E64E-4280-BDDD-65518CA462CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5C4A07-841A-4948-BCE8-DD49217FB0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E167558C-EDAE-441A-9DD3-8D69DFB345C7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E167558C-EDAE-441A-9DD3-8D69DFB345C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>Option 1: Parralel beam</t>
   </si>
@@ -47,18 +47,9 @@
     <t>mesh_to_detector (mm)</t>
   </si>
   <si>
-    <t>mesh_line_distance (mm)</t>
-  </si>
-  <si>
     <t>detector_pixelsize (mm)</t>
   </si>
   <si>
-    <t>measured_line_distance (pixels)</t>
-  </si>
-  <si>
-    <t>measured_line_distance (mm)</t>
-  </si>
-  <si>
     <t>distance_to_focalplane (mm)</t>
   </si>
   <si>
@@ -86,15 +77,9 @@
     <t>Option 2: Point source</t>
   </si>
   <si>
-    <t>point_source_to_lens (mm)</t>
-  </si>
-  <si>
     <t>distance_to_imageplane (mm)</t>
   </si>
   <si>
-    <t>image plane (mm)</t>
-  </si>
-  <si>
     <t>focal length (mm)</t>
   </si>
   <si>
@@ -102,6 +87,21 @@
   </si>
   <si>
     <t>300 mesh</t>
+  </si>
+  <si>
+    <t>Magnification</t>
+  </si>
+  <si>
+    <t>mesh_pitch_size (mm)</t>
+  </si>
+  <si>
+    <t>mesh_gap_distance (mm)</t>
+  </si>
+  <si>
+    <t>pointsource_to_lens (mm)</t>
+  </si>
+  <si>
+    <t>lens_to_imageplane (mm)</t>
   </si>
 </sst>
 </file>
@@ -152,9 +152,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -490,125 +489,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290997F1-A6F2-4FC0-8773-DC0DE9C8F7BD}">
-  <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <f>B5-B6</f>
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>5.0999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B8">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <f>B10*B8</f>
+        <v>1.925</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <f>B11/B7</f>
+        <v>19.059405940594058</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2">
-        <v>40.216999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <f>B9*B7</f>
-        <v>2.211935</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B14">
+        <f>B4/(B13-1)</f>
+        <v>6.3678728070175445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>5</v>
-      </c>
-      <c r="B11" s="1">
-        <f>B9*(B5+B6)/B5</f>
-        <v>58.354078431372542</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <f>B11*B7</f>
-        <v>3.2094743137254897</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14">
-        <f>B4/(B12/B5-1)</f>
-        <v>1.7761740140235245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>8</v>
       </c>
       <c r="B15">
         <f>B3-B14</f>
-        <v>8.2238259859764753</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8.6321271929824555</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -618,8 +620,11 @@
       <c r="C20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -629,21 +634,27 @@
       <c r="C21">
         <v>110</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B22">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="C22">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="C22">
-        <v>6.4000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B23">
         <v>2.3E-2</v>
@@ -651,226 +662,271 @@
       <c r="C23">
         <v>2.3E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <f>B22-B23</f>
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C24">
+        <f>C22-C23</f>
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="D24">
+        <f>D22-D23</f>
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C25">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D25">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1">
+        <v>56</v>
+      </c>
+      <c r="C27" s="1">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28">
+        <f>B27*B25</f>
+        <v>3.08</v>
+      </c>
+      <c r="C28">
+        <f>C27*C25</f>
+        <v>2.09</v>
+      </c>
+      <c r="D28">
+        <f>D27*D25</f>
+        <v>1.925</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <f>B28/B24</f>
+        <v>75.121951219512198</v>
+      </c>
+      <c r="C30">
+        <f>C28/C24</f>
+        <v>74.642857142857139</v>
+      </c>
+      <c r="D30">
+        <f>D28/D24</f>
+        <v>19.059405940594058</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="B24">
-        <v>5.5E-2</v>
-      </c>
-      <c r="C24">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="2">
-        <v>38</v>
-      </c>
-      <c r="C26" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="1">
-        <f>B26*B24</f>
-        <v>2.09</v>
-      </c>
-      <c r="C27" s="1">
-        <f>C26*C24</f>
-        <v>3.0249999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B31">
+        <f>B21/(B30-1)</f>
+        <v>1.4840408028956893</v>
+      </c>
+      <c r="C31">
+        <f>C21/(C30-1)</f>
+        <v>1.4936954413191077</v>
+      </c>
+      <c r="D31">
+        <f>D21/(D30-1)</f>
+        <v>6.3678728070175445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>5</v>
-      </c>
-      <c r="B28" s="1">
-        <f>B26*(B22+B23)/B22</f>
-        <v>55.137254901960787</v>
-      </c>
-      <c r="C28" s="1">
-        <f>C26*(C22+C23)/C22</f>
-        <v>74.765624999999986</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29">
-        <f>B28*B24</f>
-        <v>3.0325490196078433</v>
-      </c>
-      <c r="C29">
-        <f>C28*C24</f>
-        <v>4.1121093749999993</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31">
-        <f>B21/(B29/B22-1)</f>
-        <v>1.8815722844422229</v>
-      </c>
-      <c r="C31">
-        <f>C21/(C29/C22-1)</f>
-        <v>1.7390834455899555</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>8</v>
       </c>
       <c r="B32">
         <f>B20-B31</f>
-        <v>8.1184277155577771</v>
+        <v>8.5159591971043103</v>
       </c>
       <c r="C32">
         <f>C20-C31</f>
-        <v>8.2609165544100449</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8.5063045586808919</v>
+      </c>
+      <c r="D32">
+        <f>D20-D31</f>
+        <v>8.6321271929824555</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>1</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>2</v>
       </c>
-      <c r="B37">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <f>B39-B40</f>
+        <v>2.7999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>3</v>
       </c>
-      <c r="B38">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B42">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45">
+        <f>B44*B42</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47">
+        <f>B45/B41</f>
+        <v>196.42857142857144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48">
+        <f>B38/(B47-1)</f>
+        <v>0.74195906432748537</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49">
+        <f>B37-B48</f>
+        <v>19.258040935672515</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50">
+        <f>B49*B36/(B49+B36)</f>
+        <v>8.4321988690920744</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B39">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
         <v>16</v>
       </c>
-      <c r="B41">
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="1">
-        <f>B43*B40</f>
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="1">
-        <f>B43*(B38+B39)/B38</f>
-        <v>41.411764705882355</v>
-      </c>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46">
-        <f>B45*B40</f>
-        <v>2.2776470588235296</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48">
-        <f>B37/(B46/B38-1)</f>
-        <v>5.427230046948357</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49">
-        <f>B36-B48</f>
-        <v>14.572769953051644</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50">
-        <f>B49*B41/(B49+B41)</f>
-        <v>8.4302009777294948</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+      <c r="B54">
         <v>20</v>
       </c>
-      <c r="C54" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C54">
+        <v>20</v>
+      </c>
+      <c r="D54">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -880,8 +936,11 @@
       <c r="C55">
         <v>20</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -891,10 +950,13 @@
       <c r="C56">
         <v>140</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B57">
         <v>0.127</v>
@@ -902,10 +964,13 @@
       <c r="C57">
         <v>8.5000000000000006E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B58">
         <v>2.5999999999999999E-2</v>
@@ -913,117 +978,139 @@
       <c r="C58">
         <v>2.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B59">
+        <f>B57-B58</f>
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="C59">
+        <f>C57-C58</f>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="D59">
+        <f>D57-D58</f>
+        <v>2.7999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60">
         <v>5.5E-2</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>5.5E-2</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60">
-        <v>20</v>
-      </c>
-      <c r="C60">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="2">
-        <v>35</v>
-      </c>
-      <c r="C62" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="B62" s="1">
+        <v>34</v>
+      </c>
+      <c r="C62" s="1">
+        <v>31</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="1">
-        <f>B62*B59</f>
-        <v>1.925</v>
-      </c>
-      <c r="C63" s="1">
-        <f>C62*C59</f>
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>5</v>
-      </c>
-      <c r="B64" s="1">
-        <f>B62*(B57+B58)/B57</f>
-        <v>42.165354330708659</v>
-      </c>
-      <c r="C64" s="1">
-        <f>C62*(C57+C58)/C57</f>
-        <v>41.411764705882355</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="B63">
+        <f>B62*B60</f>
+        <v>1.87</v>
+      </c>
+      <c r="C63">
+        <f>C62*C60</f>
+        <v>1.7050000000000001</v>
+      </c>
+      <c r="D63">
+        <f>D62*D60</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B65">
-        <f>B64*B59</f>
-        <v>2.3190944881889761</v>
+        <f>B63/B59</f>
+        <v>18.514851485148515</v>
       </c>
       <c r="C65">
-        <f>C64*C59</f>
-        <v>2.2776470588235296</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+        <f>C63/C59</f>
+        <v>28.416666666666664</v>
+      </c>
+      <c r="D65">
+        <f>D63/D59</f>
+        <v>196.42857142857144</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66">
+        <f>B56/(B65-1)</f>
+        <v>5.1384963256076874</v>
+      </c>
+      <c r="C66">
+        <f>C56/(C65-1)</f>
+        <v>5.1063829787234045</v>
+      </c>
+      <c r="D66">
+        <f>D56/(D65-1)</f>
+        <v>0.74195906432748537</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B67">
-        <f>B56/(B65/B57-1)</f>
-        <v>5.2141912958519532</v>
+        <f>B55-B66</f>
+        <v>14.861503674392313</v>
       </c>
       <c r="C67">
-        <f>C56/(C65/C57-1)</f>
-        <v>5.427230046948357</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+        <f>C55-C66</f>
+        <v>14.893617021276595</v>
+      </c>
+      <c r="D67">
+        <f>D55-D66</f>
+        <v>19.258040935672515</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B68">
-        <f>B55-B67</f>
-        <v>14.785808704148046</v>
+        <f>B67*B54/(B67+B54)</f>
+        <v>8.5260256202367444</v>
       </c>
       <c r="C68">
-        <f>C55-C67</f>
-        <v>14.572769953051644</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69">
-        <f>B68*B60/(B68+B60)</f>
-        <v>8.5010579054813853</v>
-      </c>
-      <c r="C69">
-        <f>C68*C60/(C68+C60)</f>
-        <v>8.4302009777294948</v>
+        <f>C67*C54/(C67+C54)</f>
+        <v>8.5365853658536572</v>
+      </c>
+      <c r="D68">
+        <f>D67*D54/(D67+D54)</f>
+        <v>8.4321988690920744</v>
       </c>
     </row>
   </sheetData>
